--- a/TestData/Data.xlsx
+++ b/TestData/Data.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\piyun\OneDrive\Desktop\Trainings\July2025\MavenSeleniumProject\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C25AB56B-3E68-4569-A2DD-8A47FF3E2219}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{006FCC25-C795-4C7E-972D-9FF0E393FF42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BookData" sheetId="1" r:id="rId1"/>
+    <sheet name="UserData" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
   <si>
     <t>BookName</t>
   </si>
@@ -46,13 +47,40 @@
   </si>
   <si>
     <t>Priyanka</t>
+  </si>
+  <si>
+    <t>UserName</t>
+  </si>
+  <si>
+    <t>Password</t>
+  </si>
+  <si>
+    <t>test123</t>
+  </si>
+  <si>
+    <t>standard_user</t>
+  </si>
+  <si>
+    <t>secret_sauce</t>
+  </si>
+  <si>
+    <t>problem_user</t>
+  </si>
+  <si>
+    <t>Sumit</t>
+  </si>
+  <si>
+    <t>Shweta</t>
+  </si>
+  <si>
+    <t>Status</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -78,6 +106,21 @@
     <font>
       <b/>
       <sz val="22"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="20"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -119,11 +162,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -404,15 +449,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32.77734375" customWidth="1"/>
     <col min="2" max="2" width="34.44140625" customWidth="1"/>
     <col min="3" max="3" width="27.88671875" customWidth="1"/>
+    <col min="4" max="4" width="17.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:4" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -422,8 +468,11 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="D1" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -433,8 +482,11 @@
       <c r="C2" s="1">
         <v>500</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="D2" s="5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -443,6 +495,64 @@
       </c>
       <c r="C3" s="1">
         <v>1000</v>
+      </c>
+      <c r="D3" s="5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45AD61B7-5B0B-4258-B963-73B14F3D8DFC}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="35.33203125" customWidth="1"/>
+    <col min="2" max="2" width="34.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
